--- a/Headers.xlsx
+++ b/Headers.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://procdna-my.sharepoint.com/personal/jagrit_desai_procdna_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ShreerajDeshmukh\pricingtool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{98666B81-9E47-40DD-8E4A-F0F2AC365A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE0DAA9E-9BD6-49C3-8DF1-4B7ABDC5A6AB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{93BCCA26-8DFD-426E-9125-64E8D5D89AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4C80A0F3-49EC-4BAC-8431-CF004A09CC9D}"/>
+    <workbookView xWindow="2268" yWindow="2268" windowWidth="19068" windowHeight="11820" xr2:uid="{4C80A0F3-49EC-4BAC-8431-CF004A09CC9D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -210,13 +211,67 @@
   </si>
   <si>
     <t>Kindly upload approval email of Partner (PDF) and other files associated with the project</t>
+  </si>
+  <si>
+    <t>Project Code</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>Is Client New?</t>
+  </si>
+  <si>
+    <t>Project Start Date</t>
+  </si>
+  <si>
+    <t>Project End Date</t>
+  </si>
+  <si>
+    <t>Account Manager</t>
+  </si>
+  <si>
+    <t>Account Manager Email</t>
+  </si>
+  <si>
+    <t>Client Stakeholder Email</t>
+  </si>
+  <si>
+    <t>Signed Project Budget ($)</t>
+  </si>
+  <si>
+    <t>Estimated Total Hours</t>
+  </si>
+  <si>
+    <t>Discount / Premium %</t>
+  </si>
+  <si>
+    <t>Approving Partner</t>
+  </si>
+  <si>
+    <t>Line of Business</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>Gross Margin %</t>
+  </si>
+  <si>
+    <t>Offshore %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO/SoW/ Precontract aggrement </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -636,68 +691,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F942A58-DC66-4735-80DE-8F76B9866EEC}">
-  <dimension ref="A1:BE1"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:BE59"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="94.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="99.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="89.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="99.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="89.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="65.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="65.6640625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="32" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="50.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="50.109375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="18" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="46.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="52.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="51.42578125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="45.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="57.85546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="60.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="46.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="51.44140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="45.6640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="57.88671875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="47.109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="60.44140625" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="43" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="48.28515625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="61.28515625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="100.42578125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="39.140625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="45.28515625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="80.85546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="48.33203125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="61.33203125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="100.44140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="39.109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="45.33203125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="80.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -867,6 +922,354 @@
         <v>55</v>
       </c>
       <c r="BE1" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B36" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B37" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B38" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B39" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B40" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B41" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B42" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B43" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B44" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B45" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B46" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B47" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B48" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B49" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B50" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B51" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B52" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B53" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B54" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B55" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B56" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B57" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B58" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B59" s="4" t="s">
         <v>56</v>
       </c>
     </row>
